--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803036</v>
+        <v>124807161</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461666</v>
+        <v>461692</v>
       </c>
       <c r="R2" t="n">
-        <v>6787470</v>
+        <v>6787396</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124803252</v>
+        <v>124802256</v>
       </c>
       <c r="B3" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +798,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461682</v>
+        <v>461706</v>
       </c>
       <c r="R3" t="n">
-        <v>6787460</v>
+        <v>6787449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124806372</v>
+        <v>124804195</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461571</v>
+        <v>461647</v>
       </c>
       <c r="R4" t="n">
-        <v>6787397</v>
+        <v>6787435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124807196</v>
+        <v>124804916</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461748</v>
+        <v>461602</v>
       </c>
       <c r="R5" t="n">
-        <v>6787372</v>
+        <v>6787436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805748</v>
+        <v>124802715</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461602</v>
+        <v>461649</v>
       </c>
       <c r="R6" t="n">
-        <v>6787436</v>
+        <v>6787488</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1164,11 +1174,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1195,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803199</v>
+        <v>124803323</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1235,10 +1240,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461682</v>
+        <v>461668</v>
       </c>
       <c r="R7" t="n">
-        <v>6787460</v>
+        <v>6787455</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802213</v>
+        <v>124804983</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461706</v>
+        <v>461582</v>
       </c>
       <c r="R8" t="n">
-        <v>6787449</v>
+        <v>6787472</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806204</v>
+        <v>124803252</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461540</v>
+        <v>461682</v>
       </c>
       <c r="R9" t="n">
-        <v>6787386</v>
+        <v>6787460</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803451</v>
+        <v>124802985</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,24 +1527,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -1544,7 +1559,7 @@
         <v>461666</v>
       </c>
       <c r="R10" t="n">
-        <v>6787451</v>
+        <v>6787470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,11 +1592,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,7 +1618,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802776</v>
+        <v>124802240</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1648,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461658</v>
+        <v>461707</v>
       </c>
       <c r="R11" t="n">
-        <v>6787478</v>
+        <v>6787434</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1684,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,10 +1720,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803372</v>
+        <v>124805163</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1732,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461668</v>
+        <v>461591</v>
       </c>
       <c r="R12" t="n">
-        <v>6787455</v>
+        <v>6787439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804195</v>
+        <v>124806640</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1893,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124805163</v>
+        <v>124806372</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1936,25 +1936,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461591</v>
+        <v>461571</v>
       </c>
       <c r="R14" t="n">
-        <v>6787439</v>
+        <v>6787397</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802715</v>
+        <v>124805787</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461649</v>
+        <v>461602</v>
       </c>
       <c r="R15" t="n">
-        <v>6787488</v>
+        <v>6787436</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,7 +2133,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804126</v>
+        <v>124804539</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461637</v>
+        <v>461601</v>
       </c>
       <c r="R16" t="n">
-        <v>6787449</v>
+        <v>6787427</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2209,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804970</v>
+        <v>124802776</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461582</v>
+        <v>461658</v>
       </c>
       <c r="R17" t="n">
-        <v>6787472</v>
+        <v>6787478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,6 +2311,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807395</v>
+        <v>124803199</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461748</v>
+        <v>461682</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,11 +2418,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2551,7 +2551,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124807060</v>
+        <v>124803451</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461692</v>
+        <v>461666</v>
       </c>
       <c r="R20" t="n">
-        <v>6787396</v>
+        <v>6787451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2631,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2658,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804916</v>
+        <v>124806166</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2674,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2698,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461602</v>
+        <v>461540</v>
       </c>
       <c r="R21" t="n">
-        <v>6787436</v>
+        <v>6787386</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2734,11 +2734,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2765,7 +2760,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802240</v>
+        <v>124803987</v>
       </c>
       <c r="B22" t="n">
         <v>78810</v>
@@ -2805,10 +2800,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461707</v>
+        <v>461637</v>
       </c>
       <c r="R22" t="n">
-        <v>6787434</v>
+        <v>6787449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2841,6 +2836,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2867,10 +2867,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802301</v>
+        <v>124807196</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2883,21 +2883,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2907,10 +2907,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461706</v>
+        <v>461748</v>
       </c>
       <c r="R23" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,7 +2969,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806774</v>
+        <v>124803036</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R24" t="n">
-        <v>6787395</v>
+        <v>6787470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124802985</v>
+        <v>124803093</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,39 +3087,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461666</v>
+        <v>461668</v>
       </c>
       <c r="R25" t="n">
-        <v>6787470</v>
+        <v>6787455</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3152,6 +3147,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804211</v>
+        <v>124806774</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3194,21 +3194,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461647</v>
+        <v>461662</v>
       </c>
       <c r="R26" t="n">
-        <v>6787435</v>
+        <v>6787395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3254,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3285,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124804539</v>
+        <v>124807395</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3301,21 +3296,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3325,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461601</v>
+        <v>461748</v>
       </c>
       <c r="R27" t="n">
-        <v>6787427</v>
+        <v>6787372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3361,6 +3356,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3387,7 +3387,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124803093</v>
+        <v>124802301</v>
       </c>
       <c r="B28" t="n">
         <v>78547</v>
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461668</v>
+        <v>461706</v>
       </c>
       <c r="R28" t="n">
-        <v>6787455</v>
+        <v>6787449</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,11 +3463,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124807161</v>
+        <v>124806640</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461692</v>
+        <v>461647</v>
       </c>
       <c r="R2" t="n">
-        <v>6787396</v>
+        <v>6787435</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802256</v>
+        <v>124804983</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461706</v>
+        <v>461582</v>
       </c>
       <c r="R3" t="n">
-        <v>6787449</v>
+        <v>6787472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804195</v>
+        <v>124803854</v>
       </c>
       <c r="B4" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R4" t="n">
-        <v>6787435</v>
+        <v>6787451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804916</v>
+        <v>124803199</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461602</v>
+        <v>461682</v>
       </c>
       <c r="R5" t="n">
-        <v>6787436</v>
+        <v>6787460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802715</v>
+        <v>124804720</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1138,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461649</v>
+        <v>461602</v>
       </c>
       <c r="R6" t="n">
-        <v>6787488</v>
+        <v>6787436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803323</v>
+        <v>124803093</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1276,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804983</v>
+        <v>124802256</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1342,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461582</v>
+        <v>461706</v>
       </c>
       <c r="R8" t="n">
-        <v>6787472</v>
+        <v>6787449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803252</v>
+        <v>124806166</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461682</v>
+        <v>461540</v>
       </c>
       <c r="R9" t="n">
-        <v>6787460</v>
+        <v>6787386</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,11 +1475,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802240</v>
+        <v>124805163</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1630,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461707</v>
+        <v>461591</v>
       </c>
       <c r="R11" t="n">
-        <v>6787434</v>
+        <v>6787439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1720,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805163</v>
+        <v>124804916</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1732,25 +1722,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1760,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461591</v>
+        <v>461602</v>
       </c>
       <c r="R12" t="n">
-        <v>6787439</v>
+        <v>6787436</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1796,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124806640</v>
+        <v>124807161</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461647</v>
+        <v>461692</v>
       </c>
       <c r="R13" t="n">
-        <v>6787435</v>
+        <v>6787396</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806372</v>
+        <v>124802715</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1964,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461571</v>
+        <v>461649</v>
       </c>
       <c r="R14" t="n">
-        <v>6787397</v>
+        <v>6787488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124805787</v>
+        <v>124802240</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2066,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461602</v>
+        <v>461707</v>
       </c>
       <c r="R15" t="n">
-        <v>6787436</v>
+        <v>6787434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,11 +2102,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804539</v>
+        <v>124803987</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461601</v>
+        <v>461637</v>
       </c>
       <c r="R16" t="n">
-        <v>6787427</v>
+        <v>6787449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802776</v>
+        <v>124803372</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461658</v>
+        <v>461668</v>
       </c>
       <c r="R17" t="n">
-        <v>6787478</v>
+        <v>6787455</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2311,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803199</v>
+        <v>124807395</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2358,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2382,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R18" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803538</v>
+        <v>124806372</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461666</v>
+        <v>461571</v>
       </c>
       <c r="R19" t="n">
-        <v>6787451</v>
+        <v>6787397</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,11 +2520,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803451</v>
+        <v>124803252</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2567,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461666</v>
+        <v>461682</v>
       </c>
       <c r="R20" t="n">
-        <v>6787451</v>
+        <v>6787460</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2631,7 +2626,7 @@
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2658,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124806166</v>
+        <v>124802301</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2674,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2698,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461540</v>
+        <v>461706</v>
       </c>
       <c r="R21" t="n">
-        <v>6787386</v>
+        <v>6787449</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2760,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803987</v>
+        <v>124804195</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2776,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2800,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461637</v>
+        <v>461647</v>
       </c>
       <c r="R22" t="n">
-        <v>6787449</v>
+        <v>6787435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2867,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124807196</v>
+        <v>124802776</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2907,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461748</v>
+        <v>461658</v>
       </c>
       <c r="R23" t="n">
-        <v>6787372</v>
+        <v>6787478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2943,6 +2938,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2969,7 +2969,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803036</v>
+        <v>124807196</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -3009,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461666</v>
+        <v>461748</v>
       </c>
       <c r="R24" t="n">
-        <v>6787470</v>
+        <v>6787372</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803093</v>
+        <v>124803036</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461668</v>
+        <v>461666</v>
       </c>
       <c r="R25" t="n">
-        <v>6787455</v>
+        <v>6787470</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3280,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124807395</v>
+        <v>124804539</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461748</v>
+        <v>461601</v>
       </c>
       <c r="R27" t="n">
-        <v>6787372</v>
+        <v>6787427</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,11 +3351,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3387,7 +3377,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802301</v>
+        <v>124803538</v>
       </c>
       <c r="B28" t="n">
         <v>78547</v>
@@ -3427,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461706</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787449</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3463,6 +3453,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124806166</v>
+        <v>124804916</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461540</v>
+        <v>461602</v>
       </c>
       <c r="R9" t="n">
-        <v>6787386</v>
+        <v>6787436</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802985</v>
+        <v>124805163</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1513,43 +1518,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461666</v>
+        <v>461591</v>
       </c>
       <c r="R10" t="n">
-        <v>6787470</v>
+        <v>6787439</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805163</v>
+        <v>124806166</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461591</v>
+        <v>461540</v>
       </c>
       <c r="R11" t="n">
-        <v>6787439</v>
+        <v>6787386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124804916</v>
+        <v>124802985</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,34 +1726,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R12" t="n">
-        <v>6787436</v>
+        <v>6787470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -3173,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806774</v>
+        <v>124804539</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461662</v>
+        <v>461601</v>
       </c>
       <c r="R26" t="n">
-        <v>6787395</v>
+        <v>6787427</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124804539</v>
+        <v>124803538</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461601</v>
+        <v>461666</v>
       </c>
       <c r="R27" t="n">
-        <v>6787427</v>
+        <v>6787451</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,6 +3351,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124803538</v>
+        <v>124806774</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461662</v>
       </c>
       <c r="R28" t="n">
-        <v>6787451</v>
+        <v>6787395</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,11 +3458,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -3173,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804539</v>
+        <v>124806774</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461601</v>
+        <v>461662</v>
       </c>
       <c r="R26" t="n">
-        <v>6787427</v>
+        <v>6787395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124803538</v>
+        <v>124804539</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R27" t="n">
-        <v>6787451</v>
+        <v>6787427</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,11 +3351,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124806774</v>
+        <v>124803538</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,21 +3393,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787395</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3453,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124806640</v>
+        <v>124803323</v>
       </c>
       <c r="B2" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461647</v>
+        <v>461668</v>
       </c>
       <c r="R2" t="n">
-        <v>6787435</v>
+        <v>6787455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804983</v>
+        <v>124803199</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461582</v>
+        <v>461682</v>
       </c>
       <c r="R3" t="n">
-        <v>6787472</v>
+        <v>6787460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803854</v>
+        <v>124804539</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R4" t="n">
-        <v>6787451</v>
+        <v>6787427</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803199</v>
+        <v>124804211</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461682</v>
+        <v>461647</v>
       </c>
       <c r="R5" t="n">
-        <v>6787460</v>
+        <v>6787435</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804720</v>
+        <v>124806774</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461602</v>
+        <v>461662</v>
       </c>
       <c r="R6" t="n">
-        <v>6787436</v>
+        <v>6787395</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803093</v>
+        <v>124806204</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461668</v>
+        <v>461540</v>
       </c>
       <c r="R7" t="n">
-        <v>6787455</v>
+        <v>6787386</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802256</v>
+        <v>124802340</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1399,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804916</v>
+        <v>124803854</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R9" t="n">
-        <v>6787436</v>
+        <v>6787451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1474,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805163</v>
+        <v>124804746</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1518,25 +1513,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461591</v>
+        <v>461602</v>
       </c>
       <c r="R10" t="n">
-        <v>6787439</v>
+        <v>6787436</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,7 +1603,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124806166</v>
+        <v>124804983</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461540</v>
+        <v>461582</v>
       </c>
       <c r="R11" t="n">
-        <v>6787386</v>
+        <v>6787472</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802985</v>
+        <v>124807196</v>
       </c>
       <c r="B12" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,39 +1721,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461666</v>
+        <v>461748</v>
       </c>
       <c r="R12" t="n">
-        <v>6787470</v>
+        <v>6787372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,10 +1807,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124807161</v>
+        <v>124803093</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1833,21 +1823,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1847,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461692</v>
+        <v>461668</v>
       </c>
       <c r="R13" t="n">
-        <v>6787396</v>
+        <v>6787455</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1897,7 +1887,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802715</v>
+        <v>124807161</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1964,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461649</v>
+        <v>461692</v>
       </c>
       <c r="R14" t="n">
-        <v>6787488</v>
+        <v>6787396</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2000,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802240</v>
+        <v>124806294</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461707</v>
+        <v>461571</v>
       </c>
       <c r="R15" t="n">
-        <v>6787434</v>
+        <v>6787397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803987</v>
+        <v>124802776</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461637</v>
+        <v>461658</v>
       </c>
       <c r="R16" t="n">
-        <v>6787449</v>
+        <v>6787478</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803372</v>
+        <v>124802240</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461668</v>
+        <v>461707</v>
       </c>
       <c r="R17" t="n">
-        <v>6787455</v>
+        <v>6787434</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807395</v>
+        <v>124803252</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461748</v>
+        <v>461682</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787460</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2417,7 +2412,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806372</v>
+        <v>124805163</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,25 +2451,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461571</v>
+        <v>461591</v>
       </c>
       <c r="R19" t="n">
-        <v>6787397</v>
+        <v>6787439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803252</v>
+        <v>124802985</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,34 +2557,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461682</v>
+        <v>461666</v>
       </c>
       <c r="R20" t="n">
-        <v>6787460</v>
+        <v>6787470</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,11 +2622,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802301</v>
+        <v>124803036</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461706</v>
+        <v>461666</v>
       </c>
       <c r="R21" t="n">
-        <v>6787449</v>
+        <v>6787470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804195</v>
+        <v>124802301</v>
       </c>
       <c r="B22" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461647</v>
+        <v>461706</v>
       </c>
       <c r="R22" t="n">
-        <v>6787435</v>
+        <v>6787449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,11 +2826,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,7 +2852,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802776</v>
+        <v>124804126</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2902,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461658</v>
+        <v>461637</v>
       </c>
       <c r="R23" t="n">
-        <v>6787478</v>
+        <v>6787449</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2969,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124807196</v>
+        <v>124807395</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2985,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3045,6 +3035,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803036</v>
+        <v>124804916</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461666</v>
+        <v>461602</v>
       </c>
       <c r="R25" t="n">
-        <v>6787470</v>
+        <v>6787436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,6 +3142,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806774</v>
+        <v>124803538</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R26" t="n">
-        <v>6787395</v>
+        <v>6787451</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,6 +3249,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124804539</v>
+        <v>124804195</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,21 +3296,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461601</v>
+        <v>461647</v>
       </c>
       <c r="R27" t="n">
-        <v>6787427</v>
+        <v>6787435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,6 +3356,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3387,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124803538</v>
+        <v>124802715</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3403,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3427,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461649</v>
       </c>
       <c r="R28" t="n">
-        <v>6787451</v>
+        <v>6787488</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,11 +3463,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803323</v>
+        <v>124804445</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461668</v>
+        <v>461602</v>
       </c>
       <c r="R2" t="n">
-        <v>6787455</v>
+        <v>6787436</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124803199</v>
+        <v>124804126</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461682</v>
+        <v>461637</v>
       </c>
       <c r="R3" t="n">
-        <v>6787460</v>
+        <v>6787449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +884,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804539</v>
+        <v>124802256</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461601</v>
+        <v>461706</v>
       </c>
       <c r="R4" t="n">
-        <v>6787427</v>
+        <v>6787449</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804211</v>
+        <v>124803755</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R5" t="n">
-        <v>6787435</v>
+        <v>6787451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124806774</v>
+        <v>124803323</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461662</v>
+        <v>461668</v>
       </c>
       <c r="R6" t="n">
-        <v>6787395</v>
+        <v>6787455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124806204</v>
+        <v>124806294</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461540</v>
+        <v>461571</v>
       </c>
       <c r="R7" t="n">
-        <v>6787386</v>
+        <v>6787397</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802340</v>
+        <v>124803199</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461706</v>
+        <v>461682</v>
       </c>
       <c r="R8" t="n">
-        <v>6787449</v>
+        <v>6787460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803854</v>
+        <v>124804983</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461666</v>
+        <v>461582</v>
       </c>
       <c r="R9" t="n">
-        <v>6787451</v>
+        <v>6787472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,11 +1470,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1501,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804746</v>
+        <v>124806166</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1541,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461602</v>
+        <v>461540</v>
       </c>
       <c r="R10" t="n">
-        <v>6787436</v>
+        <v>6787386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1603,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804983</v>
+        <v>124803036</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1643,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461582</v>
+        <v>461666</v>
       </c>
       <c r="R11" t="n">
-        <v>6787472</v>
+        <v>6787470</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1700,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124807196</v>
+        <v>124805163</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1717,25 +1712,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461748</v>
+        <v>461591</v>
       </c>
       <c r="R12" t="n">
-        <v>6787372</v>
+        <v>6787439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1807,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803093</v>
+        <v>124803252</v>
       </c>
       <c r="B13" t="n">
         <v>78547</v>
@@ -1847,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461668</v>
+        <v>461682</v>
       </c>
       <c r="R13" t="n">
-        <v>6787455</v>
+        <v>6787460</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1887,7 +1882,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1909,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124807161</v>
+        <v>124807395</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1925,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1949,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461692</v>
+        <v>461748</v>
       </c>
       <c r="R14" t="n">
-        <v>6787396</v>
+        <v>6787372</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +1989,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806294</v>
+        <v>124802240</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2061,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461571</v>
+        <v>461707</v>
       </c>
       <c r="R15" t="n">
-        <v>6787397</v>
+        <v>6787434</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802240</v>
+        <v>124802985</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,34 +2241,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461707</v>
+        <v>461666</v>
       </c>
       <c r="R17" t="n">
-        <v>6787434</v>
+        <v>6787470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803252</v>
+        <v>124807196</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2348,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R18" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,11 +2408,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805163</v>
+        <v>124804539</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2451,25 +2446,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461591</v>
+        <v>461601</v>
       </c>
       <c r="R19" t="n">
-        <v>6787439</v>
+        <v>6787427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802985</v>
+        <v>124804195</v>
       </c>
       <c r="B20" t="n">
-        <v>57529</v>
+        <v>78546</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,39 +2552,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461666</v>
+        <v>461647</v>
       </c>
       <c r="R20" t="n">
-        <v>6787470</v>
+        <v>6787435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,6 +2612,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803036</v>
+        <v>124804916</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461666</v>
+        <v>461602</v>
       </c>
       <c r="R21" t="n">
-        <v>6787470</v>
+        <v>6787436</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,6 +2719,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802301</v>
+        <v>124803093</v>
       </c>
       <c r="B22" t="n">
         <v>78547</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461706</v>
+        <v>461668</v>
       </c>
       <c r="R22" t="n">
-        <v>6787449</v>
+        <v>6787455</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,6 +2826,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,7 +2857,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804126</v>
+        <v>124806774</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461637</v>
+        <v>461662</v>
       </c>
       <c r="R23" t="n">
-        <v>6787449</v>
+        <v>6787395</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,11 +2933,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124807395</v>
+        <v>124804211</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461748</v>
+        <v>461647</v>
       </c>
       <c r="R24" t="n">
-        <v>6787372</v>
+        <v>6787435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,7 +3066,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804916</v>
+        <v>124803538</v>
       </c>
       <c r="B25" t="n">
         <v>78547</v>
@@ -3106,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R25" t="n">
-        <v>6787436</v>
+        <v>6787451</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3146,7 +3146,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803538</v>
+        <v>124807161</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461666</v>
+        <v>461692</v>
       </c>
       <c r="R26" t="n">
-        <v>6787451</v>
+        <v>6787396</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3253,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,10 +3280,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124804195</v>
+        <v>124802301</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,21 +3296,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461647</v>
+        <v>461706</v>
       </c>
       <c r="R27" t="n">
-        <v>6787435</v>
+        <v>6787449</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,11 +3356,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -1292,7 +1292,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803199</v>
+        <v>124806166</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461682</v>
+        <v>461540</v>
       </c>
       <c r="R8" t="n">
-        <v>6787460</v>
+        <v>6787386</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,7 +1394,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804983</v>
+        <v>124802240</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1434,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461707</v>
       </c>
       <c r="R9" t="n">
-        <v>6787472</v>
+        <v>6787434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124806166</v>
+        <v>124805163</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1508,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461540</v>
+        <v>461591</v>
       </c>
       <c r="R10" t="n">
-        <v>6787386</v>
+        <v>6787439</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,10 +1598,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803036</v>
+        <v>124803252</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1614,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461666</v>
+        <v>461682</v>
       </c>
       <c r="R11" t="n">
-        <v>6787470</v>
+        <v>6787460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,6 +1674,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805163</v>
+        <v>124802776</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1712,25 +1717,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1740,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461591</v>
+        <v>461658</v>
       </c>
       <c r="R12" t="n">
-        <v>6787439</v>
+        <v>6787478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803252</v>
+        <v>124807395</v>
       </c>
       <c r="B13" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1818,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R13" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1882,7 +1892,7 @@
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1909,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124807395</v>
+        <v>124803199</v>
       </c>
       <c r="B14" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1925,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1949,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461748</v>
+        <v>461682</v>
       </c>
       <c r="R14" t="n">
-        <v>6787372</v>
+        <v>6787460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1985,11 +1995,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124802240</v>
+        <v>124804983</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461707</v>
+        <v>461582</v>
       </c>
       <c r="R15" t="n">
-        <v>6787434</v>
+        <v>6787472</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,7 +2123,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802776</v>
+        <v>124803036</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2158,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461658</v>
+        <v>461666</v>
       </c>
       <c r="R16" t="n">
-        <v>6787478</v>
+        <v>6787470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124804445</v>
+        <v>124803854</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R2" t="n">
-        <v>6787436</v>
+        <v>6787451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,6 +751,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804126</v>
+        <v>124806166</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461637</v>
+        <v>461540</v>
       </c>
       <c r="R3" t="n">
-        <v>6787449</v>
+        <v>6787386</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +858,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124802256</v>
+        <v>124806640</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461706</v>
+        <v>461647</v>
       </c>
       <c r="R4" t="n">
-        <v>6787449</v>
+        <v>6787435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803755</v>
+        <v>124804916</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461666</v>
+        <v>461602</v>
       </c>
       <c r="R5" t="n">
-        <v>6787451</v>
+        <v>6787436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1062,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1093,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803323</v>
+        <v>124803354</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1190,7 +1195,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124806294</v>
+        <v>124802240</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461571</v>
+        <v>461707</v>
       </c>
       <c r="R7" t="n">
-        <v>6787397</v>
+        <v>6787434</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1297,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124806166</v>
+        <v>124804617</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461540</v>
+        <v>461602</v>
       </c>
       <c r="R8" t="n">
-        <v>6787386</v>
+        <v>6787436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,6 +1373,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802240</v>
+        <v>124804195</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461707</v>
+        <v>461647</v>
       </c>
       <c r="R9" t="n">
-        <v>6787434</v>
+        <v>6787435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1470,6 +1480,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1496,10 +1511,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124805163</v>
+        <v>124807060</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1523,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461591</v>
+        <v>461692</v>
       </c>
       <c r="R10" t="n">
-        <v>6787439</v>
+        <v>6787396</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1572,6 +1587,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1598,10 +1618,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803252</v>
+        <v>124804539</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1614,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1638,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461682</v>
+        <v>461601</v>
       </c>
       <c r="R11" t="n">
-        <v>6787460</v>
+        <v>6787427</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1674,11 +1694,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1705,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802776</v>
+        <v>124807196</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1745,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461658</v>
+        <v>461748</v>
       </c>
       <c r="R12" t="n">
-        <v>6787478</v>
+        <v>6787372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1796,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1822,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124807395</v>
+        <v>124806774</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1838,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461748</v>
+        <v>461662</v>
       </c>
       <c r="R13" t="n">
-        <v>6787372</v>
+        <v>6787395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,7 +1924,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803199</v>
+        <v>124802715</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461682</v>
+        <v>461649</v>
       </c>
       <c r="R14" t="n">
-        <v>6787460</v>
+        <v>6787488</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804983</v>
+        <v>124803252</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461582</v>
+        <v>461682</v>
       </c>
       <c r="R15" t="n">
-        <v>6787472</v>
+        <v>6787460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,6 +2102,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2123,7 +2133,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803036</v>
+        <v>124804983</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2163,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461666</v>
+        <v>461582</v>
       </c>
       <c r="R16" t="n">
-        <v>6787470</v>
+        <v>6787472</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802985</v>
+        <v>124802256</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,39 +2251,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461666</v>
+        <v>461706</v>
       </c>
       <c r="R17" t="n">
-        <v>6787470</v>
+        <v>6787449</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807196</v>
+        <v>124805163</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2344,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461748</v>
+        <v>461591</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2434,7 +2439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804539</v>
+        <v>124803152</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461601</v>
+        <v>461682</v>
       </c>
       <c r="R19" t="n">
-        <v>6787427</v>
+        <v>6787460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2536,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804195</v>
+        <v>124806294</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461647</v>
+        <v>461571</v>
       </c>
       <c r="R20" t="n">
-        <v>6787435</v>
+        <v>6787397</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,11 +2617,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804916</v>
+        <v>124802776</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2659,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461602</v>
+        <v>461658</v>
       </c>
       <c r="R21" t="n">
-        <v>6787436</v>
+        <v>6787478</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,7 +2750,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803093</v>
+        <v>124802301</v>
       </c>
       <c r="B22" t="n">
         <v>78547</v>
@@ -2790,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461668</v>
+        <v>461706</v>
       </c>
       <c r="R22" t="n">
-        <v>6787455</v>
+        <v>6787449</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,11 +2826,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124806774</v>
+        <v>124802985</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,34 +2868,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R23" t="n">
-        <v>6787395</v>
+        <v>6787470</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,10 +2959,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804211</v>
+        <v>124803036</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,21 +2975,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R24" t="n">
-        <v>6787435</v>
+        <v>6787470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,11 +3035,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3066,7 +3061,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803538</v>
+        <v>124803093</v>
       </c>
       <c r="B25" t="n">
         <v>78547</v>
@@ -3106,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461666</v>
+        <v>461668</v>
       </c>
       <c r="R25" t="n">
-        <v>6787451</v>
+        <v>6787455</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,7 +3168,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124807161</v>
+        <v>124803987</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3213,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461692</v>
+        <v>461637</v>
       </c>
       <c r="R26" t="n">
-        <v>6787396</v>
+        <v>6787449</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3253,7 +3248,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3280,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802301</v>
+        <v>124807395</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461706</v>
+        <v>461748</v>
       </c>
       <c r="R27" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,6 +3351,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802715</v>
+        <v>124803538</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461649</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787488</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3458,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -2852,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802985</v>
+        <v>124803036</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,29 +2868,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -2959,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803036</v>
+        <v>124802985</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2975,24 +2970,29 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803854</v>
+        <v>124802240</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461666</v>
+        <v>461707</v>
       </c>
       <c r="R2" t="n">
-        <v>6787451</v>
+        <v>6787434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -751,11 +751,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124806166</v>
+        <v>124804539</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461540</v>
+        <v>461601</v>
       </c>
       <c r="R3" t="n">
-        <v>6787386</v>
+        <v>6787427</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124806640</v>
+        <v>124803755</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R4" t="n">
-        <v>6787435</v>
+        <v>6787451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804916</v>
+        <v>124805347</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1062,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803354</v>
+        <v>124802256</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1133,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461668</v>
+        <v>461706</v>
       </c>
       <c r="R6" t="n">
-        <v>6787455</v>
+        <v>6787449</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1195,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802240</v>
+        <v>124805040</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1235,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461707</v>
+        <v>461582</v>
       </c>
       <c r="R7" t="n">
-        <v>6787434</v>
+        <v>6787472</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804617</v>
+        <v>124802985</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,34 +1303,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R8" t="n">
-        <v>6787436</v>
+        <v>6787470</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,11 +1368,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i en radie av ca 50 meter.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804195</v>
+        <v>124803538</v>
       </c>
       <c r="B9" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1420,21 +1410,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1444,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R9" t="n">
-        <v>6787435</v>
+        <v>6787451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1511,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124807060</v>
+        <v>124802301</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1527,21 +1517,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1551,10 +1541,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461692</v>
+        <v>461706</v>
       </c>
       <c r="R10" t="n">
-        <v>6787396</v>
+        <v>6787449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,11 +1577,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1618,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804539</v>
+        <v>124803093</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1634,21 +1619,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1658,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461601</v>
+        <v>461668</v>
       </c>
       <c r="R11" t="n">
-        <v>6787427</v>
+        <v>6787455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1694,6 +1679,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1720,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124807196</v>
+        <v>124803036</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1760,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R12" t="n">
-        <v>6787372</v>
+        <v>6787470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1822,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124806774</v>
+        <v>124804195</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1838,21 +1828,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1862,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461662</v>
+        <v>461647</v>
       </c>
       <c r="R13" t="n">
-        <v>6787395</v>
+        <v>6787435</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1898,6 +1888,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1924,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802715</v>
+        <v>124803120</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1964,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461649</v>
+        <v>461668</v>
       </c>
       <c r="R14" t="n">
-        <v>6787488</v>
+        <v>6787455</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803252</v>
+        <v>124807395</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2042,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R15" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2106,7 +2101,7 @@
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2133,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124804983</v>
+        <v>124803199</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2173,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461582</v>
+        <v>461682</v>
       </c>
       <c r="R16" t="n">
-        <v>6787472</v>
+        <v>6787460</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2235,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802256</v>
+        <v>124806372</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2275,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461706</v>
+        <v>461571</v>
       </c>
       <c r="R17" t="n">
-        <v>6787449</v>
+        <v>6787397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805163</v>
+        <v>124807161</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461591</v>
+        <v>461692</v>
       </c>
       <c r="R18" t="n">
-        <v>6787439</v>
+        <v>6787396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2408,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803152</v>
+        <v>124807196</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R19" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124806294</v>
+        <v>124806640</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461571</v>
+        <v>461647</v>
       </c>
       <c r="R20" t="n">
-        <v>6787397</v>
+        <v>6787435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,7 +2643,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802776</v>
+        <v>124802715</v>
       </c>
       <c r="B21" t="n">
         <v>78810</v>
@@ -2683,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461658</v>
+        <v>461649</v>
       </c>
       <c r="R21" t="n">
-        <v>6787478</v>
+        <v>6787488</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,11 +2719,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2750,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802301</v>
+        <v>124806774</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461706</v>
+        <v>461662</v>
       </c>
       <c r="R22" t="n">
-        <v>6787449</v>
+        <v>6787395</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2852,7 +2847,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124803036</v>
+        <v>124802776</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2892,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461666</v>
+        <v>461658</v>
       </c>
       <c r="R23" t="n">
-        <v>6787470</v>
+        <v>6787478</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,6 +2923,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802985</v>
+        <v>124806228</v>
       </c>
       <c r="B24" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,39 +2970,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461666</v>
+        <v>461540</v>
       </c>
       <c r="R24" t="n">
-        <v>6787470</v>
+        <v>6787386</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3061,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803093</v>
+        <v>124803252</v>
       </c>
       <c r="B25" t="n">
         <v>78547</v>
@@ -3101,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461668</v>
+        <v>461682</v>
       </c>
       <c r="R25" t="n">
-        <v>6787455</v>
+        <v>6787460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3136,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803987</v>
+        <v>124804916</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3184,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3208,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461637</v>
+        <v>461602</v>
       </c>
       <c r="R26" t="n">
-        <v>6787449</v>
+        <v>6787436</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,7 +3243,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,10 +3270,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124807395</v>
+        <v>124803987</v>
       </c>
       <c r="B27" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3291,21 +3286,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461748</v>
+        <v>461637</v>
       </c>
       <c r="R27" t="n">
-        <v>6787372</v>
+        <v>6787449</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3355,7 +3350,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124803538</v>
+        <v>124805163</v>
       </c>
       <c r="B28" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3394,25 +3389,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3422,10 +3417,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461591</v>
       </c>
       <c r="R28" t="n">
-        <v>6787451</v>
+        <v>6787439</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,11 +3453,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802240</v>
+        <v>124803354</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461707</v>
+        <v>461668</v>
       </c>
       <c r="R2" t="n">
-        <v>6787434</v>
+        <v>6787455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804539</v>
+        <v>124804746</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461601</v>
+        <v>461602</v>
       </c>
       <c r="R3" t="n">
-        <v>6787427</v>
+        <v>6787436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803755</v>
+        <v>124804970</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461666</v>
+        <v>461582</v>
       </c>
       <c r="R4" t="n">
-        <v>6787451</v>
+        <v>6787472</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805347</v>
+        <v>124803538</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R5" t="n">
-        <v>6787436</v>
+        <v>6787451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124802256</v>
+        <v>124807196</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461706</v>
+        <v>461748</v>
       </c>
       <c r="R6" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124805040</v>
+        <v>124804126</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461582</v>
+        <v>461637</v>
       </c>
       <c r="R7" t="n">
-        <v>6787472</v>
+        <v>6787449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1261,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1287,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802985</v>
+        <v>124804539</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,39 +1313,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R8" t="n">
-        <v>6787470</v>
+        <v>6787427</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1394,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803538</v>
+        <v>124803451</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1410,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1501,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802301</v>
+        <v>124802776</v>
       </c>
       <c r="B10" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1517,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461706</v>
+        <v>461658</v>
       </c>
       <c r="R10" t="n">
-        <v>6787449</v>
+        <v>6787478</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803093</v>
+        <v>124803152</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461668</v>
+        <v>461682</v>
       </c>
       <c r="R11" t="n">
-        <v>6787455</v>
+        <v>6787460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1679,11 +1689,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1710,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803036</v>
+        <v>124805163</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1722,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461666</v>
+        <v>461591</v>
       </c>
       <c r="R12" t="n">
-        <v>6787470</v>
+        <v>6787439</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124804195</v>
+        <v>124803036</v>
       </c>
       <c r="B13" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1828,21 +1833,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R13" t="n">
-        <v>6787435</v>
+        <v>6787470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,11 +1893,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803120</v>
+        <v>124802301</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461668</v>
+        <v>461706</v>
       </c>
       <c r="R14" t="n">
-        <v>6787455</v>
+        <v>6787449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124807395</v>
+        <v>124806640</v>
       </c>
       <c r="B15" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2037,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461748</v>
+        <v>461647</v>
       </c>
       <c r="R15" t="n">
-        <v>6787372</v>
+        <v>6787435</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2097,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803199</v>
+        <v>124803093</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461682</v>
+        <v>461668</v>
       </c>
       <c r="R16" t="n">
-        <v>6787460</v>
+        <v>6787455</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,6 +2199,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,7 +2230,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124806372</v>
+        <v>124807161</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2270,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461571</v>
+        <v>461692</v>
       </c>
       <c r="R17" t="n">
-        <v>6787397</v>
+        <v>6787396</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,6 +2306,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2332,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807161</v>
+        <v>124807395</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2348,21 +2353,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461692</v>
+        <v>461748</v>
       </c>
       <c r="R18" t="n">
-        <v>6787396</v>
+        <v>6787372</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2412,7 +2417,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,7 +2444,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124807196</v>
+        <v>124806774</v>
       </c>
       <c r="B19" t="n">
         <v>78810</v>
@@ -2479,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461748</v>
+        <v>461662</v>
       </c>
       <c r="R19" t="n">
-        <v>6787372</v>
+        <v>6787395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124806640</v>
+        <v>124802402</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461647</v>
+        <v>461706</v>
       </c>
       <c r="R20" t="n">
-        <v>6787435</v>
+        <v>6787449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802715</v>
+        <v>124803252</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2683,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461649</v>
+        <v>461682</v>
       </c>
       <c r="R21" t="n">
-        <v>6787488</v>
+        <v>6787460</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2719,6 +2724,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806774</v>
+        <v>124804916</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461662</v>
+        <v>461602</v>
       </c>
       <c r="R22" t="n">
-        <v>6787395</v>
+        <v>6787436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2831,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,7 +2862,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802776</v>
+        <v>124802240</v>
       </c>
       <c r="B23" t="n">
         <v>78810</v>
@@ -2887,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461658</v>
+        <v>461707</v>
       </c>
       <c r="R23" t="n">
-        <v>6787478</v>
+        <v>6787434</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2923,11 +2938,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124806228</v>
+        <v>124804195</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,21 +2980,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461540</v>
+        <v>461647</v>
       </c>
       <c r="R24" t="n">
-        <v>6787386</v>
+        <v>6787435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3040,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803252</v>
+        <v>124806166</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461682</v>
+        <v>461540</v>
       </c>
       <c r="R25" t="n">
-        <v>6787460</v>
+        <v>6787386</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3132,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124804916</v>
+        <v>124806294</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3189,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461602</v>
+        <v>461571</v>
       </c>
       <c r="R26" t="n">
-        <v>6787436</v>
+        <v>6787397</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,11 +3249,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124803987</v>
+        <v>124802715</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461637</v>
+        <v>461649</v>
       </c>
       <c r="R27" t="n">
-        <v>6787449</v>
+        <v>6787488</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,11 +3351,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124805163</v>
+        <v>124802985</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3389,38 +3389,43 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461591</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787439</v>
+        <v>6787470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -3173,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806294</v>
+        <v>124802985</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,34 +3189,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461571</v>
+        <v>461666</v>
       </c>
       <c r="R26" t="n">
-        <v>6787397</v>
+        <v>6787470</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,7 +3280,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802715</v>
+        <v>124806294</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3315,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461649</v>
+        <v>461571</v>
       </c>
       <c r="R27" t="n">
-        <v>6787488</v>
+        <v>6787397</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3377,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802985</v>
+        <v>124802715</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,39 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461649</v>
       </c>
       <c r="R28" t="n">
-        <v>6787470</v>
+        <v>6787488</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803152</v>
+        <v>124805163</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461682</v>
+        <v>461591</v>
       </c>
       <c r="R11" t="n">
-        <v>6787460</v>
+        <v>6787439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124805163</v>
+        <v>124803152</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461591</v>
+        <v>461682</v>
       </c>
       <c r="R12" t="n">
-        <v>6787439</v>
+        <v>6787460</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -3173,10 +3173,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802985</v>
+        <v>124806294</v>
       </c>
       <c r="B26" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,39 +3189,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461666</v>
+        <v>461571</v>
       </c>
       <c r="R26" t="n">
-        <v>6787470</v>
+        <v>6787397</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124806294</v>
+        <v>124802715</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3320,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461571</v>
+        <v>461649</v>
       </c>
       <c r="R27" t="n">
-        <v>6787397</v>
+        <v>6787488</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3382,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802715</v>
+        <v>124802985</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,34 +3393,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461649</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787488</v>
+        <v>6787470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803354</v>
+        <v>124804944</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461668</v>
+        <v>461582</v>
       </c>
       <c r="R2" t="n">
-        <v>6787455</v>
+        <v>6787472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804746</v>
+        <v>124802256</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461602</v>
+        <v>461706</v>
       </c>
       <c r="R3" t="n">
-        <v>6787436</v>
+        <v>6787449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804970</v>
+        <v>124803372</v>
       </c>
       <c r="B4" t="n">
         <v>78810</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461582</v>
+        <v>461668</v>
       </c>
       <c r="R4" t="n">
-        <v>6787472</v>
+        <v>6787455</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803538</v>
+        <v>124806228</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461666</v>
+        <v>461540</v>
       </c>
       <c r="R5" t="n">
-        <v>6787451</v>
+        <v>6787386</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1057,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124807196</v>
+        <v>124804720</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461748</v>
+        <v>461602</v>
       </c>
       <c r="R6" t="n">
-        <v>6787372</v>
+        <v>6787436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804126</v>
+        <v>124802985</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,34 +1201,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461637</v>
+        <v>461666</v>
       </c>
       <c r="R7" t="n">
-        <v>6787449</v>
+        <v>6787470</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804539</v>
+        <v>124807395</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461601</v>
+        <v>461748</v>
       </c>
       <c r="R8" t="n">
-        <v>6787427</v>
+        <v>6787372</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1373,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803451</v>
+        <v>124807161</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461666</v>
+        <v>461692</v>
       </c>
       <c r="R9" t="n">
-        <v>6787451</v>
+        <v>6787396</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802776</v>
+        <v>124804539</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461658</v>
+        <v>461601</v>
       </c>
       <c r="R10" t="n">
-        <v>6787478</v>
+        <v>6787427</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1582,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805163</v>
+        <v>124803152</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1620,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461591</v>
+        <v>461682</v>
       </c>
       <c r="R11" t="n">
-        <v>6787439</v>
+        <v>6787460</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1710,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803152</v>
+        <v>124803451</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461682</v>
+        <v>461666</v>
       </c>
       <c r="R12" t="n">
-        <v>6787460</v>
+        <v>6787451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1786,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124803036</v>
+        <v>124805163</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461666</v>
+        <v>461591</v>
       </c>
       <c r="R13" t="n">
-        <v>6787470</v>
+        <v>6787439</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,7 +1919,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802301</v>
+        <v>124803538</v>
       </c>
       <c r="B14" t="n">
         <v>78547</v>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461706</v>
+        <v>461666</v>
       </c>
       <c r="R14" t="n">
-        <v>6787449</v>
+        <v>6787451</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,6 +1995,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,10 +2026,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806640</v>
+        <v>124806294</v>
       </c>
       <c r="B15" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2037,21 +2042,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461647</v>
+        <v>461571</v>
       </c>
       <c r="R15" t="n">
-        <v>6787435</v>
+        <v>6787397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2230,7 +2235,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807161</v>
+        <v>124802776</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2270,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461692</v>
+        <v>461658</v>
       </c>
       <c r="R17" t="n">
-        <v>6787396</v>
+        <v>6787478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2315,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,10 +2342,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807395</v>
+        <v>124802301</v>
       </c>
       <c r="B18" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2358,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461748</v>
+        <v>461706</v>
       </c>
       <c r="R18" t="n">
-        <v>6787372</v>
+        <v>6787449</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,11 +2418,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806774</v>
+        <v>124803252</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461662</v>
+        <v>461682</v>
       </c>
       <c r="R19" t="n">
-        <v>6787395</v>
+        <v>6787460</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,6 +2520,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,7 +2551,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802402</v>
+        <v>124802715</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2586,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461706</v>
+        <v>461649</v>
       </c>
       <c r="R20" t="n">
-        <v>6787449</v>
+        <v>6787488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2648,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803252</v>
+        <v>124807196</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,21 +2669,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2688,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R21" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2724,11 +2729,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,7 +2755,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804916</v>
+        <v>124806640</v>
       </c>
       <c r="B22" t="n">
         <v>78547</v>
@@ -2795,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461602</v>
+        <v>461647</v>
       </c>
       <c r="R22" t="n">
-        <v>6787436</v>
+        <v>6787435</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2831,11 +2831,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2862,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802240</v>
+        <v>124804195</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2878,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2902,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461707</v>
+        <v>461647</v>
       </c>
       <c r="R23" t="n">
-        <v>6787434</v>
+        <v>6787435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2938,6 +2933,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804195</v>
+        <v>124803036</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2980,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R24" t="n">
-        <v>6787435</v>
+        <v>6787470</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3040,11 +3040,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3071,10 +3066,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124806166</v>
+        <v>124804916</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3082,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3111,10 +3106,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461540</v>
+        <v>461602</v>
       </c>
       <c r="R25" t="n">
-        <v>6787386</v>
+        <v>6787436</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3147,6 +3142,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3173,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806294</v>
+        <v>124806774</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3213,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461571</v>
+        <v>461662</v>
       </c>
       <c r="R26" t="n">
-        <v>6787397</v>
+        <v>6787395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3275,7 +3275,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802715</v>
+        <v>124803987</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3315,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461649</v>
+        <v>461637</v>
       </c>
       <c r="R27" t="n">
-        <v>6787488</v>
+        <v>6787449</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3351,6 +3351,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802985</v>
+        <v>124802240</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,39 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461707</v>
       </c>
       <c r="R28" t="n">
-        <v>6787470</v>
+        <v>6787434</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124804944</v>
+        <v>124802402</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461582</v>
+        <v>461706</v>
       </c>
       <c r="R2" t="n">
-        <v>6787472</v>
+        <v>6787449</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124802256</v>
+        <v>124807060</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461706</v>
+        <v>461692</v>
       </c>
       <c r="R3" t="n">
-        <v>6787449</v>
+        <v>6787396</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124806228</v>
+        <v>124805887</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461540</v>
+        <v>461602</v>
       </c>
       <c r="R5" t="n">
-        <v>6787386</v>
+        <v>6787436</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804720</v>
+        <v>124804944</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461602</v>
+        <v>461582</v>
       </c>
       <c r="R6" t="n">
-        <v>6787436</v>
+        <v>6787472</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802985</v>
+        <v>124804126</v>
       </c>
       <c r="B7" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,39 +1206,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461666</v>
+        <v>461637</v>
       </c>
       <c r="R7" t="n">
-        <v>6787470</v>
+        <v>6787449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1266,6 +1266,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124807395</v>
+        <v>124803622</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R8" t="n">
-        <v>6787372</v>
+        <v>6787451</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1373,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124807161</v>
+        <v>124804211</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1415,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461692</v>
+        <v>461647</v>
       </c>
       <c r="R9" t="n">
-        <v>6787396</v>
+        <v>6787435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804539</v>
+        <v>124804195</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,21 +1522,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461601</v>
+        <v>461647</v>
       </c>
       <c r="R10" t="n">
-        <v>6787427</v>
+        <v>6787435</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1608,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803152</v>
+        <v>124805163</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1620,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461682</v>
+        <v>461591</v>
       </c>
       <c r="R11" t="n">
-        <v>6787460</v>
+        <v>6787439</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803451</v>
+        <v>124803036</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1753,7 +1758,7 @@
         <v>461666</v>
       </c>
       <c r="R12" t="n">
-        <v>6787451</v>
+        <v>6787470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,10 +1817,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124805163</v>
+        <v>124807196</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1829,25 +1829,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1857,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461591</v>
+        <v>461748</v>
       </c>
       <c r="R13" t="n">
-        <v>6787439</v>
+        <v>6787372</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1919,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803538</v>
+        <v>124806166</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1935,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1959,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461666</v>
+        <v>461540</v>
       </c>
       <c r="R14" t="n">
-        <v>6787451</v>
+        <v>6787386</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1995,11 +1995,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2026,7 +2021,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806294</v>
+        <v>124803134</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2066,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461571</v>
+        <v>461682</v>
       </c>
       <c r="R15" t="n">
-        <v>6787397</v>
+        <v>6787460</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2123,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803093</v>
+        <v>124806294</v>
       </c>
       <c r="B16" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2139,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2163,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461668</v>
+        <v>461571</v>
       </c>
       <c r="R16" t="n">
-        <v>6787455</v>
+        <v>6787397</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,11 +2199,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,7 +2225,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802776</v>
+        <v>124804539</v>
       </c>
       <c r="B17" t="n">
         <v>78810</v>
@@ -2275,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461658</v>
+        <v>461601</v>
       </c>
       <c r="R17" t="n">
-        <v>6787478</v>
+        <v>6787427</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2311,11 +2301,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2342,7 +2327,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124802301</v>
+        <v>124803538</v>
       </c>
       <c r="B18" t="n">
         <v>78547</v>
@@ -2382,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461706</v>
+        <v>461666</v>
       </c>
       <c r="R18" t="n">
-        <v>6787449</v>
+        <v>6787451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2418,6 +2403,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2434,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803252</v>
+        <v>124806774</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2460,21 +2450,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2474,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461682</v>
+        <v>461662</v>
       </c>
       <c r="R19" t="n">
-        <v>6787460</v>
+        <v>6787395</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2520,11 +2510,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2551,7 +2536,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802715</v>
+        <v>124802240</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2591,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461649</v>
+        <v>461707</v>
       </c>
       <c r="R20" t="n">
-        <v>6787488</v>
+        <v>6787434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124807196</v>
+        <v>124804916</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2669,21 +2654,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2678,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461748</v>
+        <v>461602</v>
       </c>
       <c r="R21" t="n">
-        <v>6787372</v>
+        <v>6787436</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2729,6 +2714,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2755,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806640</v>
+        <v>124802715</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,21 +2761,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2795,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461647</v>
+        <v>461649</v>
       </c>
       <c r="R22" t="n">
-        <v>6787435</v>
+        <v>6787488</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2847,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124804195</v>
+        <v>124807395</v>
       </c>
       <c r="B23" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2873,21 +2863,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2887,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461647</v>
+        <v>461748</v>
       </c>
       <c r="R23" t="n">
-        <v>6787435</v>
+        <v>6787372</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2937,7 +2927,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124803036</v>
+        <v>124802301</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461666</v>
+        <v>461706</v>
       </c>
       <c r="R24" t="n">
-        <v>6787470</v>
+        <v>6787449</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3066,7 +3056,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124804916</v>
+        <v>124803252</v>
       </c>
       <c r="B25" t="n">
         <v>78547</v>
@@ -3106,10 +3096,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461602</v>
+        <v>461682</v>
       </c>
       <c r="R25" t="n">
-        <v>6787436</v>
+        <v>6787460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3173,10 +3163,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124806774</v>
+        <v>124803093</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3189,21 +3179,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3213,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461662</v>
+        <v>461668</v>
       </c>
       <c r="R26" t="n">
-        <v>6787395</v>
+        <v>6787455</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3249,6 +3239,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3275,7 +3270,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124803987</v>
+        <v>124802776</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3315,10 +3310,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461637</v>
+        <v>461658</v>
       </c>
       <c r="R27" t="n">
-        <v>6787449</v>
+        <v>6787478</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3382,10 +3377,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802240</v>
+        <v>124802985</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3398,34 +3393,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461707</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787434</v>
+        <v>6787470</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802402</v>
+        <v>124803622</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461706</v>
+        <v>461666</v>
       </c>
       <c r="R2" t="n">
-        <v>6787449</v>
+        <v>6787451</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124807060</v>
+        <v>124805787</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461692</v>
+        <v>461602</v>
       </c>
       <c r="R3" t="n">
-        <v>6787396</v>
+        <v>6787436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803372</v>
+        <v>124804211</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461668</v>
+        <v>461647</v>
       </c>
       <c r="R4" t="n">
-        <v>6787455</v>
+        <v>6787435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,6 +960,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +991,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124805887</v>
+        <v>124803252</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461602</v>
+        <v>461682</v>
       </c>
       <c r="R5" t="n">
-        <v>6787436</v>
+        <v>6787460</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1062,6 +1067,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,7 +1098,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804944</v>
+        <v>124806372</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1128,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461582</v>
+        <v>461571</v>
       </c>
       <c r="R6" t="n">
-        <v>6787472</v>
+        <v>6787397</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1190,7 +1200,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804126</v>
+        <v>124802340</v>
       </c>
       <c r="B7" t="n">
         <v>78810</v>
@@ -1230,7 +1240,7 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461637</v>
+        <v>461706</v>
       </c>
       <c r="R7" t="n">
         <v>6787449</v>
@@ -1266,11 +1276,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1297,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803622</v>
+        <v>124803199</v>
       </c>
       <c r="B8" t="n">
         <v>78810</v>
@@ -1337,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461666</v>
+        <v>461682</v>
       </c>
       <c r="R8" t="n">
-        <v>6787451</v>
+        <v>6787460</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804211</v>
+        <v>124804970</v>
       </c>
       <c r="B9" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461647</v>
+        <v>461582</v>
       </c>
       <c r="R9" t="n">
-        <v>6787435</v>
+        <v>6787472</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124804195</v>
+        <v>124802985</v>
       </c>
       <c r="B10" t="n">
-        <v>78546</v>
+        <v>57529</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,34 +1522,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R10" t="n">
-        <v>6787435</v>
+        <v>6787470</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1582,11 +1587,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1613,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124805163</v>
+        <v>124803323</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1625,25 +1625,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461591</v>
+        <v>461668</v>
       </c>
       <c r="R11" t="n">
-        <v>6787439</v>
+        <v>6787455</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,7 +1715,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803036</v>
+        <v>124802776</v>
       </c>
       <c r="B12" t="n">
         <v>78810</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461666</v>
+        <v>461658</v>
       </c>
       <c r="R12" t="n">
-        <v>6787470</v>
+        <v>6787478</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,6 +1791,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1817,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124807196</v>
+        <v>124806204</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461748</v>
+        <v>461540</v>
       </c>
       <c r="R13" t="n">
-        <v>6787372</v>
+        <v>6787386</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1919,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806166</v>
+        <v>124802301</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1935,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1959,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461540</v>
+        <v>461706</v>
       </c>
       <c r="R14" t="n">
-        <v>6787386</v>
+        <v>6787449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2021,7 +2026,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803134</v>
+        <v>124806774</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2061,10 +2066,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461682</v>
+        <v>461662</v>
       </c>
       <c r="R15" t="n">
-        <v>6787460</v>
+        <v>6787395</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2123,7 +2128,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124806294</v>
+        <v>124803987</v>
       </c>
       <c r="B16" t="n">
         <v>78810</v>
@@ -2163,10 +2168,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461571</v>
+        <v>461637</v>
       </c>
       <c r="R16" t="n">
-        <v>6787397</v>
+        <v>6787449</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2199,6 +2204,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2327,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803538</v>
+        <v>124805163</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461666</v>
+        <v>461591</v>
       </c>
       <c r="R18" t="n">
-        <v>6787451</v>
+        <v>6787439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2434,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124806774</v>
+        <v>124803538</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2450,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2474,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R19" t="n">
-        <v>6787395</v>
+        <v>6787451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2510,6 +2515,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,7 +2546,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802240</v>
+        <v>124802715</v>
       </c>
       <c r="B20" t="n">
         <v>78810</v>
@@ -2576,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461707</v>
+        <v>461649</v>
       </c>
       <c r="R20" t="n">
-        <v>6787434</v>
+        <v>6787488</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2638,10 +2648,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124804916</v>
+        <v>124803036</v>
       </c>
       <c r="B21" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,21 +2664,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2678,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R21" t="n">
-        <v>6787436</v>
+        <v>6787470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2714,11 +2724,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2745,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802715</v>
+        <v>124804916</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2766,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2790,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461649</v>
+        <v>461602</v>
       </c>
       <c r="R22" t="n">
-        <v>6787488</v>
+        <v>6787436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,6 +2826,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2847,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124807395</v>
+        <v>124803093</v>
       </c>
       <c r="B23" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2863,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2887,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461748</v>
+        <v>461668</v>
       </c>
       <c r="R23" t="n">
-        <v>6787372</v>
+        <v>6787455</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2927,7 +2937,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,10 +2964,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802301</v>
+        <v>124804195</v>
       </c>
       <c r="B24" t="n">
-        <v>78547</v>
+        <v>78546</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2970,21 +2980,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2994,10 +3004,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461706</v>
+        <v>461647</v>
       </c>
       <c r="R24" t="n">
-        <v>6787449</v>
+        <v>6787435</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,6 +3040,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3056,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803252</v>
+        <v>124807395</v>
       </c>
       <c r="B25" t="n">
-        <v>78547</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3072,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3096,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461682</v>
+        <v>461748</v>
       </c>
       <c r="R25" t="n">
-        <v>6787460</v>
+        <v>6787372</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3136,7 +3151,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3178,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803093</v>
+        <v>124802240</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3194,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461668</v>
+        <v>461707</v>
       </c>
       <c r="R26" t="n">
-        <v>6787455</v>
+        <v>6787434</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,11 +3254,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3270,7 +3280,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802776</v>
+        <v>124807196</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3310,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461658</v>
+        <v>461748</v>
       </c>
       <c r="R27" t="n">
-        <v>6787478</v>
+        <v>6787372</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3346,11 +3356,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802985</v>
+        <v>124807060</v>
       </c>
       <c r="B28" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,39 +3398,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461666</v>
+        <v>461692</v>
       </c>
       <c r="R28" t="n">
-        <v>6787470</v>
+        <v>6787396</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3458,6 +3458,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -2235,10 +2235,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124804539</v>
+        <v>124805163</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2247,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461601</v>
+        <v>461591</v>
       </c>
       <c r="R17" t="n">
-        <v>6787427</v>
+        <v>6787439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805163</v>
+        <v>124803538</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2349,25 +2349,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461591</v>
+        <v>461666</v>
       </c>
       <c r="R18" t="n">
-        <v>6787439</v>
+        <v>6787451</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,6 +2413,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803538</v>
+        <v>124804539</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2460,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2484,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R19" t="n">
-        <v>6787451</v>
+        <v>6787427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,11 +2520,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3178,7 +3178,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802240</v>
+        <v>124807196</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3218,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461707</v>
+        <v>461748</v>
       </c>
       <c r="R26" t="n">
-        <v>6787434</v>
+        <v>6787372</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,7 +3280,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124807196</v>
+        <v>124802240</v>
       </c>
       <c r="B27" t="n">
         <v>78810</v>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461748</v>
+        <v>461707</v>
       </c>
       <c r="R27" t="n">
-        <v>6787372</v>
+        <v>6787434</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803622</v>
+        <v>124802240</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461666</v>
+        <v>461707</v>
       </c>
       <c r="R2" t="n">
-        <v>6787451</v>
+        <v>6787434</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124805787</v>
+        <v>124803134</v>
       </c>
       <c r="B3" t="n">
         <v>78810</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461602</v>
+        <v>461682</v>
       </c>
       <c r="R3" t="n">
-        <v>6787436</v>
+        <v>6787460</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804211</v>
+        <v>124806204</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461647</v>
+        <v>461540</v>
       </c>
       <c r="R4" t="n">
-        <v>6787435</v>
+        <v>6787386</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -960,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803252</v>
+        <v>124804944</v>
       </c>
       <c r="B5" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1007,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461682</v>
+        <v>461582</v>
       </c>
       <c r="R5" t="n">
-        <v>6787460</v>
+        <v>6787472</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,11 +1057,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124806372</v>
+        <v>124803372</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1138,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461571</v>
+        <v>461668</v>
       </c>
       <c r="R6" t="n">
-        <v>6787397</v>
+        <v>6787455</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1200,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124802340</v>
+        <v>124803252</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1216,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1240,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461706</v>
+        <v>461682</v>
       </c>
       <c r="R7" t="n">
-        <v>6787449</v>
+        <v>6787460</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1276,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1302,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124803199</v>
+        <v>124804916</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1318,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1342,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461682</v>
+        <v>461602</v>
       </c>
       <c r="R8" t="n">
-        <v>6787460</v>
+        <v>6787436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1378,6 +1368,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,7 +1399,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124804970</v>
+        <v>124803987</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461582</v>
+        <v>461637</v>
       </c>
       <c r="R9" t="n">
-        <v>6787472</v>
+        <v>6787449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1480,6 +1475,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,10 +1506,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124802985</v>
+        <v>124803755</v>
       </c>
       <c r="B10" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1522,29 +1522,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -1554,7 +1549,7 @@
         <v>461666</v>
       </c>
       <c r="R10" t="n">
-        <v>6787470</v>
+        <v>6787451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1613,7 +1608,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124803323</v>
+        <v>124804445</v>
       </c>
       <c r="B11" t="n">
         <v>78810</v>
@@ -1653,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461668</v>
+        <v>461602</v>
       </c>
       <c r="R11" t="n">
-        <v>6787455</v>
+        <v>6787436</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1715,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802776</v>
+        <v>124802301</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1731,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1755,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461658</v>
+        <v>461706</v>
       </c>
       <c r="R12" t="n">
-        <v>6787478</v>
+        <v>6787449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1791,11 +1786,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1822,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124806204</v>
+        <v>124802340</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1862,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461540</v>
+        <v>461706</v>
       </c>
       <c r="R13" t="n">
-        <v>6787386</v>
+        <v>6787449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1924,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124802301</v>
+        <v>124806774</v>
       </c>
       <c r="B14" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1940,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1964,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461706</v>
+        <v>461662</v>
       </c>
       <c r="R14" t="n">
-        <v>6787449</v>
+        <v>6787395</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2026,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806774</v>
+        <v>124806294</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2066,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461662</v>
+        <v>461571</v>
       </c>
       <c r="R15" t="n">
-        <v>6787395</v>
+        <v>6787397</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2128,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803987</v>
+        <v>124807395</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461637</v>
+        <v>461748</v>
       </c>
       <c r="R16" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2208,7 +2198,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2235,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124805163</v>
+        <v>124803036</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2247,25 +2237,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2275,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461591</v>
+        <v>461666</v>
       </c>
       <c r="R17" t="n">
-        <v>6787439</v>
+        <v>6787470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2337,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803538</v>
+        <v>124804539</v>
       </c>
       <c r="B18" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2353,21 +2343,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2377,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R18" t="n">
-        <v>6787451</v>
+        <v>6787427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2413,11 +2403,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2444,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804539</v>
+        <v>124805163</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2456,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2484,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461601</v>
+        <v>461591</v>
       </c>
       <c r="R19" t="n">
-        <v>6787427</v>
+        <v>6787439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2546,10 +2531,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802715</v>
+        <v>124803538</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2547,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2571,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461649</v>
+        <v>461666</v>
       </c>
       <c r="R20" t="n">
-        <v>6787488</v>
+        <v>6787451</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,6 +2607,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2648,10 +2638,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803036</v>
+        <v>124802985</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2664,24 +2654,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -2750,7 +2745,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124804916</v>
+        <v>124803093</v>
       </c>
       <c r="B22" t="n">
         <v>78547</v>
@@ -2790,10 +2785,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461602</v>
+        <v>461668</v>
       </c>
       <c r="R22" t="n">
-        <v>6787436</v>
+        <v>6787455</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2830,7 +2825,7 @@
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2857,7 +2852,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124803093</v>
+        <v>124806640</v>
       </c>
       <c r="B23" t="n">
         <v>78547</v>
@@ -2897,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461668</v>
+        <v>461647</v>
       </c>
       <c r="R23" t="n">
-        <v>6787455</v>
+        <v>6787435</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2933,11 +2928,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2964,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804195</v>
+        <v>124802776</v>
       </c>
       <c r="B24" t="n">
-        <v>78546</v>
+        <v>78810</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2980,21 +2970,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3004,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461647</v>
+        <v>461658</v>
       </c>
       <c r="R24" t="n">
-        <v>6787435</v>
+        <v>6787478</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3071,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807395</v>
+        <v>124807196</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3087,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3147,11 +3137,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3178,7 +3163,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124807196</v>
+        <v>124802715</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3218,10 +3203,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461748</v>
+        <v>461649</v>
       </c>
       <c r="R26" t="n">
-        <v>6787372</v>
+        <v>6787488</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3280,10 +3265,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124802240</v>
+        <v>124804195</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3296,21 +3281,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3320,10 +3305,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461707</v>
+        <v>461647</v>
       </c>
       <c r="R27" t="n">
-        <v>6787434</v>
+        <v>6787435</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3356,6 +3341,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3382,7 +3372,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124807060</v>
+        <v>124807161</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3462,7 +3452,7 @@
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124807395</v>
+        <v>124803036</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,21 +2134,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2158,10 +2158,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R16" t="n">
-        <v>6787372</v>
+        <v>6787470</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2194,11 +2194,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2225,10 +2220,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803036</v>
+        <v>124807395</v>
       </c>
       <c r="B17" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2236,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2260,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461666</v>
+        <v>461748</v>
       </c>
       <c r="R17" t="n">
-        <v>6787470</v>
+        <v>6787372</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2301,6 +2296,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2327,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124804539</v>
+        <v>124805163</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2339,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2367,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461601</v>
+        <v>461591</v>
       </c>
       <c r="R18" t="n">
-        <v>6787427</v>
+        <v>6787439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2429,10 +2429,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124805163</v>
+        <v>124803538</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
+        <v>78547</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2441,25 +2441,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2469,10 +2469,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461591</v>
+        <v>461666</v>
       </c>
       <c r="R19" t="n">
-        <v>6787439</v>
+        <v>6787451</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2505,6 +2505,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2531,10 +2536,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124803538</v>
+        <v>124804539</v>
       </c>
       <c r="B20" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2547,21 +2552,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2571,10 +2576,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461666</v>
+        <v>461601</v>
       </c>
       <c r="R20" t="n">
-        <v>6787451</v>
+        <v>6787427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,11 +2612,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124802240</v>
+        <v>124805040</v>
       </c>
       <c r="B2" t="n">
         <v>78810</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461707</v>
+        <v>461582</v>
       </c>
       <c r="R2" t="n">
-        <v>6787434</v>
+        <v>6787472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124803134</v>
+        <v>124805163</v>
       </c>
       <c r="B3" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461682</v>
+        <v>461591</v>
       </c>
       <c r="R3" t="n">
-        <v>6787460</v>
+        <v>6787439</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124806204</v>
+        <v>124804211</v>
       </c>
       <c r="B4" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461540</v>
+        <v>461647</v>
       </c>
       <c r="R4" t="n">
-        <v>6787386</v>
+        <v>6787435</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124804944</v>
+        <v>124803622</v>
       </c>
       <c r="B5" t="n">
         <v>78810</v>
@@ -1021,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461582</v>
+        <v>461666</v>
       </c>
       <c r="R5" t="n">
-        <v>6787472</v>
+        <v>6787451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124803372</v>
+        <v>124805347</v>
       </c>
       <c r="B6" t="n">
         <v>78810</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461668</v>
+        <v>461602</v>
       </c>
       <c r="R6" t="n">
-        <v>6787455</v>
+        <v>6787436</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803252</v>
+        <v>124804126</v>
       </c>
       <c r="B7" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461682</v>
+        <v>461637</v>
       </c>
       <c r="R7" t="n">
-        <v>6787460</v>
+        <v>6787449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1270,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1292,10 +1297,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804916</v>
+        <v>124802776</v>
       </c>
       <c r="B8" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1308,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1332,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461602</v>
+        <v>461658</v>
       </c>
       <c r="R8" t="n">
-        <v>6787436</v>
+        <v>6787478</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1372,7 +1377,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Miljöbilder</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,7 +1404,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124803987</v>
+        <v>124807196</v>
       </c>
       <c r="B9" t="n">
         <v>78810</v>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461637</v>
+        <v>461748</v>
       </c>
       <c r="R9" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1475,11 +1480,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1506,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124803755</v>
+        <v>124806228</v>
       </c>
       <c r="B10" t="n">
         <v>78810</v>
@@ -1546,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461666</v>
+        <v>461540</v>
       </c>
       <c r="R10" t="n">
-        <v>6787451</v>
+        <v>6787386</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1608,10 +1608,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124804445</v>
+        <v>124802301</v>
       </c>
       <c r="B11" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1624,21 +1624,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461602</v>
+        <v>461706</v>
       </c>
       <c r="R11" t="n">
-        <v>6787436</v>
+        <v>6787449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1710,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124802301</v>
+        <v>124806372</v>
       </c>
       <c r="B12" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1726,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1750,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461706</v>
+        <v>461571</v>
       </c>
       <c r="R12" t="n">
-        <v>6787449</v>
+        <v>6787397</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1812,7 +1812,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802340</v>
+        <v>124802256</v>
       </c>
       <c r="B13" t="n">
         <v>78810</v>
@@ -1914,7 +1914,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124806774</v>
+        <v>124803199</v>
       </c>
       <c r="B14" t="n">
         <v>78810</v>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461662</v>
+        <v>461682</v>
       </c>
       <c r="R14" t="n">
-        <v>6787395</v>
+        <v>6787460</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2016,7 +2016,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124806294</v>
+        <v>124803120</v>
       </c>
       <c r="B15" t="n">
         <v>78810</v>
@@ -2056,10 +2056,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461571</v>
+        <v>461668</v>
       </c>
       <c r="R15" t="n">
-        <v>6787397</v>
+        <v>6787455</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124803036</v>
+        <v>124802985</v>
       </c>
       <c r="B16" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,24 +2134,29 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -2220,10 +2225,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124807395</v>
+        <v>124803538</v>
       </c>
       <c r="B17" t="n">
-        <v>57529</v>
+        <v>78547</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2236,21 +2241,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2260,10 +2265,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R17" t="n">
-        <v>6787372</v>
+        <v>6787451</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2300,7 +2305,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2327,10 +2332,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124805163</v>
+        <v>124807161</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2339,25 +2344,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2367,10 +2372,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461591</v>
+        <v>461692</v>
       </c>
       <c r="R18" t="n">
-        <v>6787439</v>
+        <v>6787396</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2403,6 +2408,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2429,7 +2439,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124803538</v>
+        <v>124804916</v>
       </c>
       <c r="B19" t="n">
         <v>78547</v>
@@ -2469,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461666</v>
+        <v>461602</v>
       </c>
       <c r="R19" t="n">
-        <v>6787451</v>
+        <v>6787436</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2509,7 +2519,7 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2536,10 +2546,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804539</v>
+        <v>124804195</v>
       </c>
       <c r="B20" t="n">
-        <v>78810</v>
+        <v>78546</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2552,21 +2562,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2576,10 +2586,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461601</v>
+        <v>461647</v>
       </c>
       <c r="R20" t="n">
-        <v>6787427</v>
+        <v>6787435</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2612,6 +2622,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2638,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802985</v>
+        <v>124803036</v>
       </c>
       <c r="B21" t="n">
-        <v>57529</v>
+        <v>78810</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,29 +2669,24 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
@@ -2745,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124803093</v>
+        <v>124806774</v>
       </c>
       <c r="B22" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2785,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461668</v>
+        <v>461662</v>
       </c>
       <c r="R22" t="n">
-        <v>6787455</v>
+        <v>6787395</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,11 +2831,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2857,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124806640</v>
+        <v>124802240</v>
       </c>
       <c r="B23" t="n">
-        <v>78547</v>
+        <v>78810</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2868,21 +2873,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2897,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461647</v>
+        <v>461707</v>
       </c>
       <c r="R23" t="n">
-        <v>6787435</v>
+        <v>6787434</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2954,7 +2959,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124802776</v>
+        <v>124804539</v>
       </c>
       <c r="B24" t="n">
         <v>78810</v>
@@ -2994,10 +2999,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461658</v>
+        <v>461601</v>
       </c>
       <c r="R24" t="n">
-        <v>6787478</v>
+        <v>6787427</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3035,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807196</v>
+        <v>124807395</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>57529</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3137,6 +3137,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3163,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124802715</v>
+        <v>124803252</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>78547</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3179,21 +3184,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3203,10 +3208,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461649</v>
+        <v>461682</v>
       </c>
       <c r="R26" t="n">
-        <v>6787488</v>
+        <v>6787460</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3239,6 +3244,11 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3265,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124804195</v>
+        <v>124803093</v>
       </c>
       <c r="B27" t="n">
-        <v>78546</v>
+        <v>78547</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3281,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3305,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461647</v>
+        <v>461668</v>
       </c>
       <c r="R27" t="n">
-        <v>6787435</v>
+        <v>6787455</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3372,7 +3382,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124807161</v>
+        <v>124802715</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3412,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461692</v>
+        <v>461649</v>
       </c>
       <c r="R28" t="n">
-        <v>6787396</v>
+        <v>6787488</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3448,11 +3458,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124805040</v>
+        <v>124803323</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461582</v>
+        <v>461668</v>
       </c>
       <c r="R2" t="n">
-        <v>6787472</v>
+        <v>6787455</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124805163</v>
+        <v>124804944</v>
       </c>
       <c r="B3" t="n">
-        <v>98101</v>
+        <v>78947</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461591</v>
+        <v>461582</v>
       </c>
       <c r="R3" t="n">
-        <v>6787439</v>
+        <v>6787472</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124804211</v>
+        <v>124803622</v>
       </c>
       <c r="B4" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461647</v>
+        <v>461666</v>
       </c>
       <c r="R4" t="n">
-        <v>6787435</v>
+        <v>6787451</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,11 +955,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124803622</v>
+        <v>124802402</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461666</v>
+        <v>461706</v>
       </c>
       <c r="R5" t="n">
-        <v>6787451</v>
+        <v>6787449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1088,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124805347</v>
+        <v>124804445</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124804126</v>
+        <v>124803538</v>
       </c>
       <c r="B7" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461637</v>
+        <v>461666</v>
       </c>
       <c r="R7" t="n">
-        <v>6787449</v>
+        <v>6787451</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1297,10 +1292,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124802776</v>
+        <v>124804916</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>78684</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1313,21 +1308,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1337,10 +1332,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461658</v>
+        <v>461602</v>
       </c>
       <c r="R8" t="n">
-        <v>6787478</v>
+        <v>6787436</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1377,7 +1372,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1404,10 +1399,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124807196</v>
+        <v>124802240</v>
       </c>
       <c r="B9" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1444,10 +1439,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461748</v>
+        <v>461707</v>
       </c>
       <c r="R9" t="n">
-        <v>6787372</v>
+        <v>6787434</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1506,10 +1501,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124806228</v>
+        <v>124806166</v>
       </c>
       <c r="B10" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1608,10 +1603,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124802301</v>
+        <v>124806640</v>
       </c>
       <c r="B11" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1648,10 +1643,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461706</v>
+        <v>461647</v>
       </c>
       <c r="R11" t="n">
-        <v>6787449</v>
+        <v>6787435</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1710,10 +1705,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124806372</v>
+        <v>124807395</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1726,21 +1721,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1750,10 +1745,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461571</v>
+        <v>461748</v>
       </c>
       <c r="R12" t="n">
-        <v>6787397</v>
+        <v>6787372</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1786,6 +1781,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,10 +1812,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802256</v>
+        <v>124806774</v>
       </c>
       <c r="B13" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1852,10 +1852,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461706</v>
+        <v>461662</v>
       </c>
       <c r="R13" t="n">
-        <v>6787449</v>
+        <v>6787395</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1914,10 +1914,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124803199</v>
+        <v>124804195</v>
       </c>
       <c r="B14" t="n">
-        <v>78810</v>
+        <v>78683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1930,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1954,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461682</v>
+        <v>461647</v>
       </c>
       <c r="R14" t="n">
-        <v>6787460</v>
+        <v>6787435</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1990,6 +1990,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2016,10 +2021,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124803120</v>
+        <v>124804126</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2056,10 +2061,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461668</v>
+        <v>461637</v>
       </c>
       <c r="R15" t="n">
-        <v>6787455</v>
+        <v>6787449</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2092,6 +2097,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2118,10 +2128,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124802985</v>
+        <v>124806294</v>
       </c>
       <c r="B16" t="n">
-        <v>57529</v>
+        <v>78947</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2134,39 +2144,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461666</v>
+        <v>461571</v>
       </c>
       <c r="R16" t="n">
-        <v>6787470</v>
+        <v>6787397</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2225,10 +2230,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124803538</v>
+        <v>124802776</v>
       </c>
       <c r="B17" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2241,21 +2246,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2265,10 +2270,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461666</v>
+        <v>461658</v>
       </c>
       <c r="R17" t="n">
-        <v>6787451</v>
+        <v>6787478</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2332,10 +2337,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124807161</v>
+        <v>124803036</v>
       </c>
       <c r="B18" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2372,10 +2377,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461692</v>
+        <v>461666</v>
       </c>
       <c r="R18" t="n">
-        <v>6787396</v>
+        <v>6787470</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2408,11 +2413,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2439,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804916</v>
+        <v>124802301</v>
       </c>
       <c r="B19" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461602</v>
+        <v>461706</v>
       </c>
       <c r="R19" t="n">
-        <v>6787436</v>
+        <v>6787449</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2515,11 +2515,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804195</v>
+        <v>124804539</v>
       </c>
       <c r="B20" t="n">
-        <v>78546</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2562,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2586,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461647</v>
+        <v>461601</v>
       </c>
       <c r="R20" t="n">
-        <v>6787435</v>
+        <v>6787427</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2622,11 +2617,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2653,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124803036</v>
+        <v>124807196</v>
       </c>
       <c r="B21" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2693,10 +2683,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461666</v>
+        <v>461748</v>
       </c>
       <c r="R21" t="n">
-        <v>6787470</v>
+        <v>6787372</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2755,10 +2745,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124806774</v>
+        <v>124802985</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>57632</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2771,34 +2761,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461662</v>
+        <v>461666</v>
       </c>
       <c r="R22" t="n">
-        <v>6787395</v>
+        <v>6787470</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2857,10 +2852,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124802240</v>
+        <v>124805163</v>
       </c>
       <c r="B23" t="n">
-        <v>78810</v>
+        <v>98269</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2869,25 +2864,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2897,10 +2892,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461707</v>
+        <v>461591</v>
       </c>
       <c r="R23" t="n">
-        <v>6787434</v>
+        <v>6787439</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2959,10 +2954,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124804539</v>
+        <v>124807161</v>
       </c>
       <c r="B24" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2999,10 +2994,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461601</v>
+        <v>461692</v>
       </c>
       <c r="R24" t="n">
-        <v>6787427</v>
+        <v>6787396</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3035,6 +3030,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3061,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124807395</v>
+        <v>124803252</v>
       </c>
       <c r="B25" t="n">
-        <v>57529</v>
+        <v>78684</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3077,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3101,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461748</v>
+        <v>461682</v>
       </c>
       <c r="R25" t="n">
-        <v>6787372</v>
+        <v>6787460</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3141,7 +3141,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Miljöbilder för området.</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,10 +3168,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803252</v>
+        <v>124803152</v>
       </c>
       <c r="B26" t="n">
-        <v>78547</v>
+        <v>78947</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3184,21 +3184,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3244,11 +3244,6 @@
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3278,7 +3273,7 @@
         <v>124803093</v>
       </c>
       <c r="B27" t="n">
-        <v>78547</v>
+        <v>78684</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3385,7 +3380,7 @@
         <v>124802715</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>78947</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -2439,10 +2439,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124802301</v>
+        <v>124804539</v>
       </c>
       <c r="B19" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2455,21 +2455,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2479,10 +2479,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461706</v>
+        <v>461601</v>
       </c>
       <c r="R19" t="n">
-        <v>6787449</v>
+        <v>6787427</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2541,10 +2541,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124804539</v>
+        <v>124802301</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2557,21 +2557,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461601</v>
+        <v>461706</v>
       </c>
       <c r="R20" t="n">
-        <v>6787427</v>
+        <v>6787449</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2643,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124807196</v>
+        <v>124802985</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,34 +2659,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R21" t="n">
-        <v>6787372</v>
+        <v>6787470</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2745,10 +2750,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124802985</v>
+        <v>124807196</v>
       </c>
       <c r="B22" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2761,39 +2766,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461666</v>
+        <v>461748</v>
       </c>
       <c r="R22" t="n">
-        <v>6787470</v>
+        <v>6787372</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124803323</v>
+        <v>124804983</v>
       </c>
       <c r="B2" t="n">
         <v>78947</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461668</v>
+        <v>461582</v>
       </c>
       <c r="R2" t="n">
-        <v>6787455</v>
+        <v>6787472</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124804944</v>
+        <v>124805887</v>
       </c>
       <c r="B3" t="n">
         <v>78947</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461582</v>
+        <v>461602</v>
       </c>
       <c r="R3" t="n">
-        <v>6787472</v>
+        <v>6787436</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124803622</v>
+        <v>124803071</v>
       </c>
       <c r="B4" t="n">
         <v>78947</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461666</v>
+        <v>461668</v>
       </c>
       <c r="R4" t="n">
-        <v>6787451</v>
+        <v>6787455</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -981,7 +986,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124802402</v>
+        <v>124802213</v>
       </c>
       <c r="B5" t="n">
         <v>78947</v>
@@ -1083,7 +1088,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124804445</v>
+        <v>124803451</v>
       </c>
       <c r="B6" t="n">
         <v>78947</v>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>461602</v>
+        <v>461666</v>
       </c>
       <c r="R6" t="n">
-        <v>6787436</v>
+        <v>6787451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1159,6 +1164,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1195,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124803538</v>
+        <v>124804195</v>
       </c>
       <c r="B7" t="n">
-        <v>78684</v>
+        <v>78683</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1211,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1235,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461666</v>
+        <v>461647</v>
       </c>
       <c r="R7" t="n">
-        <v>6787451</v>
+        <v>6787435</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1292,7 +1302,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124804916</v>
+        <v>124802301</v>
       </c>
       <c r="B8" t="n">
         <v>78684</v>
@@ -1332,10 +1342,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>461602</v>
+        <v>461706</v>
       </c>
       <c r="R8" t="n">
-        <v>6787436</v>
+        <v>6787449</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1368,11 +1378,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1399,10 +1404,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124802240</v>
+        <v>124806640</v>
       </c>
       <c r="B9" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1415,21 +1420,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1439,10 +1444,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>461707</v>
+        <v>461647</v>
       </c>
       <c r="R9" t="n">
-        <v>6787434</v>
+        <v>6787435</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1501,7 +1506,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124806166</v>
+        <v>124804126</v>
       </c>
       <c r="B10" t="n">
         <v>78947</v>
@@ -1541,10 +1546,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461540</v>
+        <v>461637</v>
       </c>
       <c r="R10" t="n">
-        <v>6787386</v>
+        <v>6787449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1577,6 +1582,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1603,10 +1613,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124806640</v>
+        <v>124806228</v>
       </c>
       <c r="B11" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1619,21 +1629,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1643,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461647</v>
+        <v>461540</v>
       </c>
       <c r="R11" t="n">
-        <v>6787435</v>
+        <v>6787386</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1705,10 +1715,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124807395</v>
+        <v>124803036</v>
       </c>
       <c r="B12" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1721,21 +1731,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1745,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461748</v>
+        <v>461666</v>
       </c>
       <c r="R12" t="n">
-        <v>6787372</v>
+        <v>6787470</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1781,11 +1791,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1812,7 +1817,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124806774</v>
+        <v>124802776</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1852,10 +1857,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461662</v>
+        <v>461658</v>
       </c>
       <c r="R13" t="n">
-        <v>6787395</v>
+        <v>6787478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1888,6 +1893,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1914,10 +1924,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124804195</v>
+        <v>124804916</v>
       </c>
       <c r="B14" t="n">
-        <v>78683</v>
+        <v>78684</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1930,21 +1940,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1954,10 +1964,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461647</v>
+        <v>461602</v>
       </c>
       <c r="R14" t="n">
-        <v>6787435</v>
+        <v>6787436</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1994,7 +2004,7 @@
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2021,7 +2031,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124804126</v>
+        <v>124807196</v>
       </c>
       <c r="B15" t="n">
         <v>78947</v>
@@ -2061,10 +2071,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461637</v>
+        <v>461748</v>
       </c>
       <c r="R15" t="n">
-        <v>6787449</v>
+        <v>6787372</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2097,11 +2107,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2128,10 +2133,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124806294</v>
+        <v>124807395</v>
       </c>
       <c r="B16" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2144,21 +2149,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2168,10 +2173,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>461571</v>
+        <v>461748</v>
       </c>
       <c r="R16" t="n">
-        <v>6787397</v>
+        <v>6787372</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2204,6 +2209,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2230,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802776</v>
+        <v>124802985</v>
       </c>
       <c r="B17" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,34 +2256,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461658</v>
+        <v>461666</v>
       </c>
       <c r="R17" t="n">
-        <v>6787478</v>
+        <v>6787470</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2306,11 +2321,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2337,7 +2347,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124803036</v>
+        <v>124806294</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2377,10 +2387,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461666</v>
+        <v>461571</v>
       </c>
       <c r="R18" t="n">
-        <v>6787470</v>
+        <v>6787397</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2541,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802301</v>
+        <v>124805163</v>
       </c>
       <c r="B20" t="n">
-        <v>78684</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2553,25 +2563,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2581,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461706</v>
+        <v>461591</v>
       </c>
       <c r="R20" t="n">
-        <v>6787449</v>
+        <v>6787439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2643,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802985</v>
+        <v>124802240</v>
       </c>
       <c r="B21" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2659,39 +2669,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461666</v>
+        <v>461707</v>
       </c>
       <c r="R21" t="n">
-        <v>6787470</v>
+        <v>6787434</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2750,10 +2755,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124807196</v>
+        <v>124803093</v>
       </c>
       <c r="B22" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2766,21 +2771,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2790,10 +2795,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461748</v>
+        <v>461668</v>
       </c>
       <c r="R22" t="n">
-        <v>6787372</v>
+        <v>6787455</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2826,6 +2831,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2852,10 +2862,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124805163</v>
+        <v>124803252</v>
       </c>
       <c r="B23" t="n">
-        <v>98269</v>
+        <v>78684</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2864,25 +2874,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2892,10 +2902,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461591</v>
+        <v>461682</v>
       </c>
       <c r="R23" t="n">
-        <v>6787439</v>
+        <v>6787460</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2928,6 +2938,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2954,7 +2969,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124807161</v>
+        <v>124803134</v>
       </c>
       <c r="B24" t="n">
         <v>78947</v>
@@ -2994,10 +3009,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>461692</v>
+        <v>461682</v>
       </c>
       <c r="R24" t="n">
-        <v>6787396</v>
+        <v>6787460</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3030,11 +3045,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3061,10 +3071,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124803252</v>
+        <v>124802715</v>
       </c>
       <c r="B25" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3077,21 +3087,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3101,10 +3111,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>461682</v>
+        <v>461649</v>
       </c>
       <c r="R25" t="n">
-        <v>6787460</v>
+        <v>6787488</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3137,11 +3147,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Miljöbilder</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3168,7 +3173,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124803152</v>
+        <v>124806774</v>
       </c>
       <c r="B26" t="n">
         <v>78947</v>
@@ -3208,10 +3213,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>461682</v>
+        <v>461662</v>
       </c>
       <c r="R26" t="n">
-        <v>6787460</v>
+        <v>6787395</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3270,10 +3275,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124803093</v>
+        <v>124807060</v>
       </c>
       <c r="B27" t="n">
-        <v>78684</v>
+        <v>78947</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3286,21 +3291,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3310,10 +3315,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>461668</v>
+        <v>461692</v>
       </c>
       <c r="R27" t="n">
-        <v>6787455</v>
+        <v>6787396</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3350,7 +3355,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Miljöbild</t>
+          <t>Miljöbilder för området.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3377,10 +3382,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124802715</v>
+        <v>124803538</v>
       </c>
       <c r="B28" t="n">
-        <v>78947</v>
+        <v>78684</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3393,21 +3398,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3417,10 +3422,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>461649</v>
+        <v>461666</v>
       </c>
       <c r="R28" t="n">
-        <v>6787488</v>
+        <v>6787451</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3453,6 +3458,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD28" t="b">

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -1613,7 +1613,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124806228</v>
+        <v>124802776</v>
       </c>
       <c r="B11" t="n">
         <v>78947</v>
@@ -1653,10 +1653,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>461540</v>
+        <v>461658</v>
       </c>
       <c r="R11" t="n">
-        <v>6787386</v>
+        <v>6787478</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1689,6 +1689,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1715,7 +1720,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124803036</v>
+        <v>124806228</v>
       </c>
       <c r="B12" t="n">
         <v>78947</v>
@@ -1755,10 +1760,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461666</v>
+        <v>461540</v>
       </c>
       <c r="R12" t="n">
-        <v>6787470</v>
+        <v>6787386</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1817,7 +1822,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124802776</v>
+        <v>124803036</v>
       </c>
       <c r="B13" t="n">
         <v>78947</v>
@@ -1857,10 +1862,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461658</v>
+        <v>461666</v>
       </c>
       <c r="R13" t="n">
-        <v>6787478</v>
+        <v>6787470</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1893,11 +1898,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Miljöbild</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124802985</v>
+        <v>124806294</v>
       </c>
       <c r="B17" t="n">
-        <v>57632</v>
+        <v>78947</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2256,39 +2256,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461666</v>
+        <v>461571</v>
       </c>
       <c r="R17" t="n">
-        <v>6787470</v>
+        <v>6787397</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2347,7 +2342,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124806294</v>
+        <v>124804539</v>
       </c>
       <c r="B18" t="n">
         <v>78947</v>
@@ -2387,10 +2382,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461571</v>
+        <v>461601</v>
       </c>
       <c r="R18" t="n">
-        <v>6787397</v>
+        <v>6787427</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2449,10 +2444,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124804539</v>
+        <v>124802985</v>
       </c>
       <c r="B19" t="n">
-        <v>78947</v>
+        <v>57632</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2465,34 +2460,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Våmån, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>461601</v>
+        <v>461666</v>
       </c>
       <c r="R19" t="n">
-        <v>6787427</v>
+        <v>6787470</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124805163</v>
+        <v>124802240</v>
       </c>
       <c r="B20" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461591</v>
+        <v>461707</v>
       </c>
       <c r="R20" t="n">
-        <v>6787439</v>
+        <v>6787434</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124802240</v>
+        <v>124805163</v>
       </c>
       <c r="B21" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,25 +2665,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461707</v>
+        <v>461591</v>
       </c>
       <c r="R21" t="n">
-        <v>6787434</v>
+        <v>6787439</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 25750-2021 artfynd.xlsx
+++ b/artfynd/A 25750-2021 artfynd.xlsx
@@ -2551,10 +2551,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124802240</v>
+        <v>124805163</v>
       </c>
       <c r="B20" t="n">
-        <v>78947</v>
+        <v>98269</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2563,25 +2563,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2591,10 +2591,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461707</v>
+        <v>461591</v>
       </c>
       <c r="R20" t="n">
-        <v>6787434</v>
+        <v>6787439</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2653,10 +2653,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124805163</v>
+        <v>124802240</v>
       </c>
       <c r="B21" t="n">
-        <v>98269</v>
+        <v>78947</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2665,25 +2665,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2693,10 +2693,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461591</v>
+        <v>461707</v>
       </c>
       <c r="R21" t="n">
-        <v>6787439</v>
+        <v>6787434</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
